--- a/danh_sach_sv.xlsx
+++ b/danh_sach_sv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anti_git\student_management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA78DCAF-7433-4624-90A5-28E9E070F701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164CDF9E-0B36-4CFF-ABD5-7C604CDFA56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>Student ID</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>Nguyễn Huy</t>
+  </si>
+  <si>
+    <t>abc</t>
   </si>
 </sst>
 </file>
@@ -423,10 +426,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -440,7 +443,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -453,8 +456,11 @@
       <c r="D2" t="s">
         <v>7</v>
       </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>

--- a/danh_sach_sv.xlsx
+++ b/danh_sach_sv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anti_git\student_management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164CDF9E-0B36-4CFF-ABD5-7C604CDFA56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB2A1B1-9B2B-45B0-9139-809032EE9C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>Student ID</t>
   </si>
@@ -473,6 +473,9 @@
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
